--- a/Data/Sheets/community_areas_details.xlsx
+++ b/Data/Sheets/community_areas_details.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\muhammad_arsalan\teesmith176\Data\Sheets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Fiverr\teesmith176\Data\Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E532E581-7D56-49B1-9BCC-2605E258086A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8E5BC0F-8D77-4C26-B59F-85CBCE60D952}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{15BEA52E-A8F4-410B-8004-6D5AD03F3055}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{15BEA52E-A8F4-410B-8004-6D5AD03F3055}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,12 +29,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="39">
   <si>
     <t>Precinct Key</t>
   </si>
@@ -133,19 +136,43 @@
   </si>
   <si>
     <t>2204700014A</t>
+  </si>
+  <si>
+    <t>Black %</t>
+  </si>
+  <si>
+    <t>White %</t>
+  </si>
+  <si>
+    <t>Other %</t>
+  </si>
+  <si>
+    <t>Women %</t>
+  </si>
+  <si>
+    <t>Men %</t>
+  </si>
+  <si>
+    <t>Voters Registered</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF222325"/>
+      <name val="Helvetica"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -168,8 +195,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -188,9 +216,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -228,7 +256,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -334,7 +362,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -476,7 +504,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -484,16 +512,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D9224A3-86D9-4666-B373-0EA9318825FF}">
-  <dimension ref="A1:D19"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:J19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.77734375" customWidth="1"/>
-    <col min="4" max="4" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.7109375" customWidth="1"/>
+    <col min="4" max="4" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -506,8 +540,26 @@
       <c r="D1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -521,7 +573,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -534,8 +586,26 @@
       <c r="D3">
         <v>946</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E3">
+        <v>632</v>
+      </c>
+      <c r="F3">
+        <v>81.5</v>
+      </c>
+      <c r="G3">
+        <v>15.7</v>
+      </c>
+      <c r="H3">
+        <v>2.8</v>
+      </c>
+      <c r="I3">
+        <v>55.1</v>
+      </c>
+      <c r="J3">
+        <v>44.9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -548,8 +618,26 @@
       <c r="D4">
         <v>980</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E4">
+        <v>862</v>
+      </c>
+      <c r="F4">
+        <v>92.2</v>
+      </c>
+      <c r="G4">
+        <v>6.7</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>54.3</v>
+      </c>
+      <c r="J4">
+        <v>45.7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -562,8 +650,26 @@
       <c r="D5">
         <v>242</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E5">
+        <v>45</v>
+      </c>
+      <c r="F5">
+        <v>24.4</v>
+      </c>
+      <c r="G5">
+        <v>75.599999999999994</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>53.3</v>
+      </c>
+      <c r="J5">
+        <v>46.7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -576,8 +682,26 @@
       <c r="D6">
         <v>807</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E6" s="1">
+        <v>673</v>
+      </c>
+      <c r="F6">
+        <v>82.9</v>
+      </c>
+      <c r="G6">
+        <v>16</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>53</v>
+      </c>
+      <c r="J6">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -590,8 +714,26 @@
       <c r="D7">
         <v>1298</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E7">
+        <v>1000</v>
+      </c>
+      <c r="F7">
+        <v>17.3</v>
+      </c>
+      <c r="G7">
+        <v>79.7</v>
+      </c>
+      <c r="H7">
+        <v>3</v>
+      </c>
+      <c r="I7">
+        <v>52.4</v>
+      </c>
+      <c r="J7">
+        <v>47.6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -604,8 +746,26 @@
       <c r="D8">
         <v>4409</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E8">
+        <v>1063</v>
+      </c>
+      <c r="F8">
+        <v>40.5</v>
+      </c>
+      <c r="G8">
+        <v>54.2</v>
+      </c>
+      <c r="H8">
+        <v>5.4</v>
+      </c>
+      <c r="I8">
+        <v>54.5</v>
+      </c>
+      <c r="J8">
+        <v>45.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -618,8 +778,26 @@
       <c r="D9">
         <v>1742</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E9">
+        <v>1183</v>
+      </c>
+      <c r="F9">
+        <v>86.4</v>
+      </c>
+      <c r="G9">
+        <v>10.8</v>
+      </c>
+      <c r="H9">
+        <v>2.8</v>
+      </c>
+      <c r="I9">
+        <v>59</v>
+      </c>
+      <c r="J9">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -632,8 +810,26 @@
       <c r="D10">
         <v>42</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E10">
+        <v>137</v>
+      </c>
+      <c r="F10">
+        <v>66.400000000000006</v>
+      </c>
+      <c r="G10">
+        <v>23.4</v>
+      </c>
+      <c r="H10">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="I10">
+        <v>43.8</v>
+      </c>
+      <c r="J10">
+        <v>56.2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -646,8 +842,26 @@
       <c r="D11">
         <v>881</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E11">
+        <v>688</v>
+      </c>
+      <c r="F11">
+        <v>97.8</v>
+      </c>
+      <c r="G11">
+        <v>0.9</v>
+      </c>
+      <c r="H11">
+        <v>1.3</v>
+      </c>
+      <c r="I11">
+        <v>58.6</v>
+      </c>
+      <c r="J11">
+        <v>41.4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -660,8 +874,26 @@
       <c r="D12">
         <v>882</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E12">
+        <v>983</v>
+      </c>
+      <c r="F12">
+        <v>92.3</v>
+      </c>
+      <c r="G12">
+        <v>6.5</v>
+      </c>
+      <c r="H12">
+        <v>1.2</v>
+      </c>
+      <c r="I12">
+        <v>56.5</v>
+      </c>
+      <c r="J12">
+        <v>43.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -674,8 +906,26 @@
       <c r="D13">
         <v>853</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E13">
+        <v>610</v>
+      </c>
+      <c r="F13">
+        <v>81.3</v>
+      </c>
+      <c r="G13">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="H13">
+        <v>1.8</v>
+      </c>
+      <c r="I13">
+        <v>57.4</v>
+      </c>
+      <c r="J13">
+        <v>42.6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>22</v>
       </c>
@@ -683,7 +933,7 @@
         <v>22047000020</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>23</v>
       </c>
@@ -691,7 +941,7 @@
         <v>22047000021</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -699,7 +949,7 @@
         <v>22047000022</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -707,7 +957,7 @@
         <v>22047000023</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>26</v>
       </c>
@@ -715,7 +965,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>27</v>
       </c>
@@ -728,8 +978,27 @@
       <c r="D19">
         <v>485</v>
       </c>
+      <c r="E19">
+        <v>578</v>
+      </c>
+      <c r="F19">
+        <v>85.3</v>
+      </c>
+      <c r="G19">
+        <v>12.6</v>
+      </c>
+      <c r="H19">
+        <v>2.1</v>
+      </c>
+      <c r="I19">
+        <v>56.7</v>
+      </c>
+      <c r="J19">
+        <v>43.3</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>